--- a/data/trans_dic/P3A_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,15</t>
+          <t>2,98; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,14</t>
+          <t>4,52; 9,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,46</t>
+          <t>3,17; 7,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,74</t>
+          <t>3,27; 11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,71</t>
+          <t>3,75; 8,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,73</t>
+          <t>5,73; 10,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 14,24</t>
+          <t>7,92; 14,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,18</t>
+          <t>5,01; 12,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,66</t>
+          <t>3,79; 6,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,1</t>
+          <t>5,58; 9,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,84</t>
+          <t>6,16; 9,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,39</t>
+          <t>4,84; 10,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,74; 31,85</t>
+          <t>25,0; 31,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,97; 31,82</t>
+          <t>25,26; 32,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,18; 41,17</t>
+          <t>33,29; 41,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,45; 35,46</t>
+          <t>23,9; 34,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,45; 27,51</t>
+          <t>20,76; 27,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,48; 30,94</t>
+          <t>22,89; 29,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,71; 29,73</t>
+          <t>22,7; 30,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 27,18</t>
+          <t>13,08; 27,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,82; 28,59</t>
+          <t>23,93; 28,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,1; 30,29</t>
+          <t>24,96; 30,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,48; 34,87</t>
+          <t>29,14; 34,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,45</t>
+          <t>18,85; 28,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,5; 33,54</t>
+          <t>25,95; 32,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,82; 47,39</t>
+          <t>39,86; 47,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,94; 50,8</t>
+          <t>42,82; 50,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,97; 48,62</t>
+          <t>39,41; 48,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 18,06</t>
+          <t>12,54; 18,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,5; 24,87</t>
+          <t>18,35; 24,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,59; 36,62</t>
+          <t>29,69; 36,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,6; 38,77</t>
+          <t>26,15; 38,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,95; 24,37</t>
+          <t>19,97; 24,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,86; 34,94</t>
+          <t>29,83; 35,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,42; 42,85</t>
+          <t>37,46; 42,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,54; 42,33</t>
+          <t>34,07; 42,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 24,93</t>
+          <t>17,4; 25,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 37,76</t>
+          <t>29,55; 37,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,3; 41,8</t>
+          <t>34,12; 42,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,02; 34,53</t>
+          <t>10,57; 34,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,82</t>
+          <t>4,89; 9,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 15,67</t>
+          <t>10,04; 15,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 22,83</t>
+          <t>16,56; 22,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 31,42</t>
+          <t>24,07; 31,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,43</t>
+          <t>12,09; 16,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,68; 25,93</t>
+          <t>20,47; 25,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,52</t>
+          <t>26,02; 31,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 31,72</t>
+          <t>16,06; 31,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 17,41</t>
+          <t>10,39; 17,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,21; 31,16</t>
+          <t>21,68; 30,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,33; 38,32</t>
+          <t>29,29; 38,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,84; 35,19</t>
+          <t>27,83; 35,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,14</t>
+          <t>5,79; 11,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,04</t>
+          <t>8,31; 14,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 16,64</t>
+          <t>10,22; 16,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,42; 23,38</t>
+          <t>18,19; 23,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 13,1</t>
+          <t>8,51; 13,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,4</t>
+          <t>15,97; 21,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,43; 26,2</t>
+          <t>20,52; 25,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,72; 28,49</t>
+          <t>23,95; 28,3</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 28,93</t>
+          <t>18,83; 28,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,72; 27,35</t>
+          <t>17,67; 27,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,03; 32,72</t>
+          <t>22,8; 32,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,92; 31,62</t>
+          <t>23,74; 31,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,9; 15,02</t>
+          <t>8,84; 15,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,1</t>
+          <t>5,71; 11,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,0</t>
+          <t>7,36; 13,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,73</t>
+          <t>3,17; 13,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,67; 20,67</t>
+          <t>14,66; 20,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,25; 18,24</t>
+          <t>12,37; 17,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 21,39</t>
+          <t>15,92; 21,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 20,65</t>
+          <t>7,79; 20,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 21,54</t>
+          <t>11,81; 21,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 18,11</t>
+          <t>9,1; 18,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,24; 22,51</t>
+          <t>14,29; 23,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,03; 23,81</t>
+          <t>16,27; 23,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,35</t>
+          <t>2,69; 7,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,69</t>
+          <t>3,14; 7,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,14</t>
+          <t>2,14; 7,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,22</t>
+          <t>4,23; 7,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 11,58</t>
+          <t>6,67; 11,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,83</t>
+          <t>6,32; 11,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 12,27</t>
+          <t>7,46; 12,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,32</t>
+          <t>9,55; 13,1</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,39; 22,27</t>
+          <t>19,56; 22,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,89; 29,0</t>
+          <t>25,84; 29,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,85; 34,21</t>
+          <t>30,71; 34,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,19; 29,56</t>
+          <t>21,24; 29,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,14</t>
+          <t>11,0; 13,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,57; 16,09</t>
+          <t>13,71; 16,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,28; 19,96</t>
+          <t>17,24; 19,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,65</t>
+          <t>15,97; 21,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,22</t>
+          <t>15,48; 17,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,02; 22,05</t>
+          <t>20,05; 22,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,19; 26,37</t>
+          <t>24,2; 26,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,2; 25,03</t>
+          <t>20,28; 25,16</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14919; 35306</t>
+          <t>14747; 35717</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19391; 41502</t>
+          <t>20527; 41960</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12851; 31139</t>
+          <t>13228; 29624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13874; 46939</t>
+          <t>13062; 47494</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17518; 35993</t>
+          <t>17509; 37371</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24475; 46148</t>
+          <t>24640; 46292</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31410; 56364</t>
+          <t>31338; 57382</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16182; 41271</t>
+          <t>15677; 39606</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36006; 64006</t>
+          <t>36374; 66071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49391; 80444</t>
+          <t>49379; 79702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49030; 80022</t>
+          <t>50092; 81126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33145; 74091</t>
+          <t>34543; 72548</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>181991; 234248</t>
+          <t>183874; 234418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>171591; 218644</t>
+          <t>173550; 220864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>195917; 243129</t>
+          <t>196601; 243568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99328; 150192</t>
+          <t>101214; 147199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127346; 171349</t>
+          <t>129292; 171694</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>143304; 188788</t>
+          <t>139703; 182845</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127761; 167283</t>
+          <t>127717; 168887</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72565; 139207</t>
+          <t>66993; 141984</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323531; 388273</t>
+          <t>325092; 390878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>325591; 392951</t>
+          <t>323846; 390362</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>339944; 402132</t>
+          <t>336065; 399993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>180958; 275502</t>
+          <t>176405; 271058</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>169016; 213896</t>
+          <t>165536; 210408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>271523; 323122</t>
+          <t>271801; 321860</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>286167; 338526</t>
+          <t>285381; 336624</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>214377; 260781</t>
+          <t>211348; 260161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85862; 124597</t>
+          <t>86476; 126361</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>131349; 176538</t>
+          <t>130237; 175746</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>195400; 241844</t>
+          <t>196076; 244327</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151557; 229525</t>
+          <t>154829; 230184</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>264864; 323498</t>
+          <t>265083; 327220</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>415519; 486265</t>
+          <t>415121; 488272</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>496451; 568560</t>
+          <t>497066; 566384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>378470; 477593</t>
+          <t>384427; 478198</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88963; 129408</t>
+          <t>90314; 130639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>182491; 232096</t>
+          <t>181598; 232826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220655; 268907</t>
+          <t>219486; 271523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97864; 306541</t>
+          <t>93812; 308998</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27575; 50651</t>
+          <t>25192; 50413</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60983; 96552</t>
+          <t>61852; 97154</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106002; 147966</t>
+          <t>107307; 147825</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>171657; 223801</t>
+          <t>171442; 225337</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122482; 170020</t>
+          <t>125146; 170706</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>254503; 319124</t>
+          <t>251905; 313737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>340854; 407038</t>
+          <t>335982; 404439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>250884; 507585</t>
+          <t>256934; 508589</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38691; 67325</t>
+          <t>40190; 66545</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95134; 133478</t>
+          <t>92861; 132274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140175; 183159</t>
+          <t>139969; 184206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156234; 197502</t>
+          <t>156183; 201514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23316; 44900</t>
+          <t>23333; 44664</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37833; 67350</t>
+          <t>37210; 65860</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50823; 82468</t>
+          <t>50676; 83565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100944; 128093</t>
+          <t>99637; 128405</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68790; 103458</t>
+          <t>67174; 103303</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140316; 187470</t>
+          <t>139894; 185440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>198932; 255075</t>
+          <t>199777; 252199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>263133; 315959</t>
+          <t>265628; 313863</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55094; 84657</t>
+          <t>55107; 84230</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54894; 84718</t>
+          <t>54738; 84262</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76749; 109060</t>
+          <t>75975; 108619</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87794; 116072</t>
+          <t>87153; 115080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30509; 51510</t>
+          <t>30329; 52699</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20018; 42714</t>
+          <t>20166; 42003</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28711; 52760</t>
+          <t>27744; 50615</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22579; 83475</t>
+          <t>19291; 83387</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93234; 131377</t>
+          <t>93196; 129946</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81217; 120866</t>
+          <t>82008; 118155</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110502; 151864</t>
+          <t>113058; 153560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>75041; 201312</t>
+          <t>75897; 200516</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24642; 45215</t>
+          <t>24785; 45190</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23450; 45260</t>
+          <t>22725; 45597</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36488; 57673</t>
+          <t>36609; 59082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45328; 67320</t>
+          <t>46018; 67310</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8815; 24532</t>
+          <t>8991; 24434</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11407; 29900</t>
+          <t>12201; 30482</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8444; 28558</t>
+          <t>8583; 28934</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17909; 30760</t>
+          <t>18022; 30805</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36602; 62950</t>
+          <t>36280; 63320</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39987; 69213</t>
+          <t>40358; 71139</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49892; 80564</t>
+          <t>48998; 79404</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>67764; 94364</t>
+          <t>67680; 92805</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>635310; 729493</t>
+          <t>640571; 736856</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>886882; 993468</t>
+          <t>885148; 996643</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1044449; 1158096</t>
+          <t>1039782; 1155736</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>732759; 1022406</t>
+          <t>734467; 1027734</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>367940; 443267</t>
+          <t>371045; 445792</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>482746; 572044</t>
+          <t>487569; 570891</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>611538; 706442</t>
+          <t>610279; 703337</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>604305; 803283</t>
+          <t>592589; 809525</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1031181; 1145058</t>
+          <t>1029471; 1154499</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1397854; 1539790</t>
+          <t>1400238; 1548024</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1674992; 1826342</t>
+          <t>1676119; 1828966</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1448600; 1794625</t>
+          <t>1453819; 1803776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,23</t>
+          <t>2,99; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,24</t>
+          <t>4,3; 8,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,09</t>
+          <t>3,05; 7,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,87</t>
+          <t>3,2; 11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,01</t>
+          <t>3,75; 8,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,76</t>
+          <t>5,65; 10,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 14,5</t>
+          <t>7,89; 14,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 12,65</t>
+          <t>4,4; 11,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,88</t>
+          <t>3,86; 6,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,01</t>
+          <t>5,54; 8,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,97</t>
+          <t>6,02; 9,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,17</t>
+          <t>4,72; 9,79</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,0; 31,87</t>
+          <t>25,25; 32,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,26; 32,14</t>
+          <t>24,92; 31,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,29; 41,25</t>
+          <t>33,24; 41,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,9; 34,75</t>
+          <t>22,18; 33,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,76; 27,57</t>
+          <t>20,62; 27,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 29,96</t>
+          <t>23,76; 31,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,7; 30,02</t>
+          <t>22,82; 30,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,08; 27,73</t>
+          <t>20,82; 28,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,93; 28,78</t>
+          <t>24,05; 28,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,96; 30,09</t>
+          <t>25,02; 29,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,14; 34,69</t>
+          <t>29,14; 34,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 28,97</t>
+          <t>22,44; 29,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,95; 32,99</t>
+          <t>26,13; 33,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,86; 47,2</t>
+          <t>39,22; 47,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,82; 50,51</t>
+          <t>42,75; 50,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,41; 48,51</t>
+          <t>38,95; 47,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 18,32</t>
+          <t>12,45; 17,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,35; 24,76</t>
+          <t>18,48; 24,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 36,99</t>
+          <t>29,68; 36,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,15; 38,88</t>
+          <t>32,7; 39,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,97; 24,65</t>
+          <t>20,02; 24,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 35,08</t>
+          <t>29,77; 34,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,46; 42,69</t>
+          <t>37,16; 42,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,07; 42,38</t>
+          <t>36,82; 42,06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 25,16</t>
+          <t>17,47; 24,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,55; 37,88</t>
+          <t>29,21; 37,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,12; 42,21</t>
+          <t>34,26; 42,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 34,81</t>
+          <t>30,49; 38,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,78</t>
+          <t>5,39; 10,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,77</t>
+          <t>10,33; 16,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 22,81</t>
+          <t>16,56; 22,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,07; 31,64</t>
+          <t>26,7; 31,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,5</t>
+          <t>11,81; 16,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 25,49</t>
+          <t>20,31; 25,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,02; 31,32</t>
+          <t>25,96; 31,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 31,79</t>
+          <t>29,33; 33,9</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,21</t>
+          <t>10,46; 17,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,68; 30,88</t>
+          <t>22,2; 30,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 38,54</t>
+          <t>29,22; 38,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,83; 35,91</t>
+          <t>28,0; 34,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,08</t>
+          <t>5,73; 10,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,31; 14,71</t>
+          <t>8,45; 15,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 16,86</t>
+          <t>10,05; 16,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,44</t>
+          <t>18,46; 23,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,08</t>
+          <t>8,62; 13,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 21,16</t>
+          <t>16,13; 21,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,52; 25,9</t>
+          <t>20,62; 26,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 28,3</t>
+          <t>24,14; 28,57</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,83; 28,79</t>
+          <t>19,57; 29,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,2</t>
+          <t>18,09; 27,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,8; 32,59</t>
+          <t>23,09; 33,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,74; 31,35</t>
+          <t>23,81; 31,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,37</t>
+          <t>8,49; 15,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 11,9</t>
+          <t>5,8; 12,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,43</t>
+          <t>7,15; 13,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 13,72</t>
+          <t>10,67; 15,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,66; 20,45</t>
+          <t>14,61; 20,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 17,83</t>
+          <t>12,3; 18,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,92; 21,63</t>
+          <t>15,79; 21,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 20,57</t>
+          <t>17,75; 22,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,81; 21,53</t>
+          <t>11,64; 22,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 18,25</t>
+          <t>9,26; 18,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,29; 23,06</t>
+          <t>14,26; 22,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,27; 23,8</t>
+          <t>15,45; 23,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,32</t>
+          <t>2,43; 7,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,84</t>
+          <t>3,13; 7,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,23</t>
+          <t>2,14; 7,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,23</t>
+          <t>4,14; 7,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,64</t>
+          <t>6,51; 11,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,14</t>
+          <t>6,23; 10,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,1</t>
+          <t>7,34; 12,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 13,1</t>
+          <t>9,31; 12,97</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,49</t>
+          <t>19,52; 22,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,84; 29,09</t>
+          <t>25,79; 29,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,71; 34,14</t>
+          <t>30,9; 34,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,24; 29,71</t>
+          <t>27,31; 30,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,21</t>
+          <t>10,89; 13,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,71; 16,05</t>
+          <t>13,77; 16,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,24; 19,87</t>
+          <t>17,19; 19,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,97; 21,81</t>
+          <t>20,1; 22,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,48; 17,36</t>
+          <t>15,46; 17,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,05; 22,17</t>
+          <t>20,1; 22,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,2; 26,41</t>
+          <t>24,29; 26,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,28; 25,16</t>
+          <t>24,01; 26,1</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>52039</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14747; 35717</t>
+          <t>14786; 35411</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20527; 41960</t>
+          <t>19547; 40109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13228; 29624</t>
+          <t>12747; 30129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13062; 47494</t>
+          <t>13048; 48392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17509; 37371</t>
+          <t>17513; 37418</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24640; 46292</t>
+          <t>24301; 47039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31338; 57382</t>
+          <t>31235; 55500</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15677; 39606</t>
+          <t>15943; 41907</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36374; 66071</t>
+          <t>37037; 66006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49379; 79702</t>
+          <t>49010; 79420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50092; 81126</t>
+          <t>48993; 79144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34543; 72548</t>
+          <t>36350; 75447</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122108</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>114006</t>
+          <t>123143</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>236114</t>
+          <t>252738</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>183874; 234418</t>
+          <t>185696; 236013</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173550; 220864</t>
+          <t>171229; 219390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196601; 243568</t>
+          <t>196271; 244604</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101214; 147199</t>
+          <t>105797; 158123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>129292; 171694</t>
+          <t>128428; 170850</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>139703; 182845</t>
+          <t>144994; 191059</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127717; 168887</t>
+          <t>128386; 168814</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66993; 141984</t>
+          <t>104480; 143513</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>325092; 390878</t>
+          <t>326642; 390987</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323846; 390362</t>
+          <t>324546; 388507</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>336065; 399993</t>
+          <t>336058; 402117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>176405; 271058</t>
+          <t>219563; 285318</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236897</t>
+          <t>268035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>204035</t>
+          <t>224145</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>440932</t>
+          <t>492180</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>165536; 210408</t>
+          <t>166635; 213687</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>271801; 321860</t>
+          <t>267425; 322675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285381; 336624</t>
+          <t>284859; 338581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>211348; 260161</t>
+          <t>241807; 294271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86476; 126361</t>
+          <t>85847; 123047</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>130237; 175746</t>
+          <t>131171; 176715</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>196076; 244327</t>
+          <t>196028; 243611</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>154829; 230184</t>
+          <t>203776; 245961</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>265083; 327220</t>
+          <t>265823; 326463</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>415121; 488272</t>
+          <t>414304; 484178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>497066; 566384</t>
+          <t>493090; 567544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>384427; 478198</t>
+          <t>458005; 523231</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214530</t>
+          <t>238732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>201669</t>
+          <t>214195</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>416198</t>
+          <t>452927</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90314; 130639</t>
+          <t>90693; 129673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>181598; 232826</t>
+          <t>179519; 228910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219486; 271523</t>
+          <t>220404; 270233</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93812; 308998</t>
+          <t>213594; 266977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25192; 50413</t>
+          <t>27801; 52726</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61852; 97154</t>
+          <t>63663; 99759</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107307; 147825</t>
+          <t>107334; 148013</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>171442; 225337</t>
+          <t>196583; 235093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125146; 170706</t>
+          <t>122195; 169635</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>251905; 313737</t>
+          <t>250006; 314792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>335982; 404439</t>
+          <t>335242; 403864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>256934; 508589</t>
+          <t>421416; 487109</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177074</t>
+          <t>192479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>113932</t>
+          <t>127506</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>291006</t>
+          <t>319985</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40190; 66545</t>
+          <t>40466; 67888</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92861; 132274</t>
+          <t>95093; 132623</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139969; 184206</t>
+          <t>139655; 183699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156183; 201514</t>
+          <t>170615; 213134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23333; 44664</t>
+          <t>23099; 43940</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37210; 65860</t>
+          <t>37852; 67583</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50676; 83565</t>
+          <t>49824; 82336</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99637; 128405</t>
+          <t>112383; 144684</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67174; 103303</t>
+          <t>68072; 103762</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>139894; 185440</t>
+          <t>141330; 191542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199777; 252199</t>
+          <t>200785; 256511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>265628; 313863</t>
+          <t>294013; 348054</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100159</t>
+          <t>110847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>56377</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>152438</t>
+          <t>167223</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55107; 84230</t>
+          <t>57244; 87021</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54738; 84262</t>
+          <t>56038; 85342</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75975; 108619</t>
+          <t>76940; 111223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87153; 115080</t>
+          <t>96671; 128012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30329; 52699</t>
+          <t>29100; 52582</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20166; 42003</t>
+          <t>20478; 42843</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27744; 50615</t>
+          <t>26924; 50847</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19291; 83387</t>
+          <t>46816; 67057</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93196; 129946</t>
+          <t>92832; 130208</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82008; 118155</t>
+          <t>81548; 119842</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113058; 153560</t>
+          <t>112156; 152581</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>75897; 200516</t>
+          <t>149938; 185793</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55883</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79698</t>
+          <t>85188</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24785; 45190</t>
+          <t>24439; 46574</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22725; 45597</t>
+          <t>23140; 46008</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36609; 59082</t>
+          <t>36547; 58299</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46018; 67310</t>
+          <t>47940; 72174</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8991; 24434</t>
+          <t>8105; 24172</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12201; 30482</t>
+          <t>12168; 31076</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8583; 28934</t>
+          <t>8571; 28751</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18022; 30805</t>
+          <t>19230; 33158</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36280; 63320</t>
+          <t>35386; 62330</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40358; 71139</t>
+          <t>39823; 67851</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48998; 79404</t>
+          <t>48151; 80226</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>67680; 92805</t>
+          <t>72117; 100484</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>932230</t>
+          <t>1025259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>735328</t>
+          <t>797020</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1667558</t>
+          <t>1822280</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>640571; 736856</t>
+          <t>639436; 734655</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>885148; 996643</t>
+          <t>883601; 998295</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1039782; 1155736</t>
+          <t>1046073; 1157803</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>734467; 1027734</t>
+          <t>964591; 1085978</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>371045; 445792</t>
+          <t>367576; 444153</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>487569; 570891</t>
+          <t>489634; 579077</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>610279; 703337</t>
+          <t>608342; 703798</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>592589; 809525</t>
+          <t>750751; 837236</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1029471; 1154499</t>
+          <t>1027807; 1148678</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1400238; 1548024</t>
+          <t>1403293; 1543968</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1676119; 1828966</t>
+          <t>1681725; 1826660</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1453819; 1803776</t>
+          <t>1744970; 1897108</t>
         </is>
       </c>
     </row>
